--- a/SensWear-V1R1-Debug/Output/Manufacturing/Assembly/Bill of Materials/Bill of Materials-SensWear-V1R1-Debug.xlsx
+++ b/SensWear-V1R1-Debug/Output/Manufacturing/Assembly/Bill of Materials/Bill of Materials-SensWear-V1R1-Debug.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORK\Projects\OpenRing\Hardware\SensWear-V1R1-Debug\Output\Manufacturing\Assembly\Bill of Materials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{29E4E93F-A8B8-4B40-8047-5EA7C4174899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B9BD5ED-B0D9-4534-9BE5-DEC1500E9DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{0095868F-BBED-45E2-925F-32AB9115B55C}"/>
+    <workbookView xWindow="43980" yWindow="1755" windowWidth="28800" windowHeight="15285" xr2:uid="{12AF83E0-F3A7-477B-9D87-1ACA8C451BB4}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-SensWear-V1R1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="91">
   <si>
     <t>Manufacturer</t>
   </si>
@@ -282,6 +282,21 @@
   </si>
   <si>
     <t>160-1409-1-ND</t>
+  </si>
+  <si>
+    <t>ON Semiconductor</t>
+  </si>
+  <si>
+    <t>MBR140SFT1G</t>
+  </si>
+  <si>
+    <t>D81</t>
+  </si>
+  <si>
+    <t>DIODE SCHOTTKY 40V 1A SOD123L</t>
+  </si>
+  <si>
+    <t>MBR140SFT1GOSDKR-ND</t>
   </si>
   <si>
     <t>Samtec</t>
@@ -692,8 +707,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4305373E-3441-4007-A031-31AD14DE2212}">
-  <dimension ref="A1:I15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F6C41A3-0C32-43BF-8480-A3C0A416835E}">
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" customWidth="1"/>
@@ -1106,7 +1121,7 @@
         <v>83</v>
       </c>
       <c r="D15" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="2" t="s">
@@ -1116,10 +1131,37 @@
         <v>84</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
